--- a/resources/report/60/95/ex_04ss/HD_04SS.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SKYPE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vng-304\einvoicevn.com\resources\report\60\95\ex_04ss\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -38,27 +38,9 @@
     <t>Chúng tôi cam kết hoàn toàn chịu trách nhiệm trước pháp luật về tính chính xác, trung thực của nội dung nêu trên và thực hiện theo đúng quy định của pháp luật.</t>
   </si>
   <si>
-    <t>Nhơn Trạch, ngày 14 tháng 11 năm 2022</t>
-  </si>
-  <si>
     <t>NGƯỜI NỘP THUẾ</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Được ký bởi: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CÔNG TY TNHH DAE YOUNG TEXTILE VIỆT NAM</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Mã số thuế: </t>
   </si>
   <si>
@@ -93,13 +75,16 @@
   </si>
   <si>
     <t xml:space="preserve">Mẫu số: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Được ký bởi: </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +126,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -320,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -349,12 +340,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -379,9 +364,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -397,71 +379,89 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,6 +478,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>282466</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>137948</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>823749</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>120495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4311541" y="3757448"/>
+          <a:ext cx="541283" cy="363547"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -750,7 +799,7 @@
     <col min="1" max="2" width="1.7109375" style="4" customWidth="1"/>
     <col min="3" max="3" width="2.5703125" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.85546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" style="4" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" style="4" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" style="4" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" style="4" customWidth="1"/>
@@ -762,17 +811,17 @@
   <sheetData>
     <row r="1" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="22"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -783,101 +832,101 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
+      <c r="H2" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:15" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
+      <c r="B5" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
+      <c r="B6" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="23"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -892,131 +941,131 @@
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
+      <c r="B9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
+      <c r="B10" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:15" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="29" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="27"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="32" t="s">
+      <c r="I12" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="J12" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="K12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="L12" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="24"/>
+      <c r="M12" s="21"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
     </row>
     <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="31"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="32"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="47"/>
       <c r="D14" s="43"/>
       <c r="E14" s="44"/>
       <c r="F14" s="45"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1026,89 +1075,71 @@
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="13"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="11"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
+      <c r="A18" s="10"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
-      <c r="M18" s="13"/>
+      <c r="M18" s="11"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="17"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="15"/>
     </row>
     <row r="20" spans="1:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:13" s="14" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:13" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:13" s="14" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:13" s="12" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:13" s="12" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:J10"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="H12:H13"/>
+  <mergeCells count="21">
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="L12:L13"/>
@@ -1119,9 +1150,21 @@
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="H12:H13"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/resources/report/60/95/ex_04ss/HD_04SS.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS.xlsx
@@ -311,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -378,6 +378,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -478,55 +484,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>282466</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>137948</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>823749</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>120495</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4311541" y="3757448"/>
-          <a:ext cx="541283" cy="363547"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -817,9 +774,9 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="3"/>
@@ -832,96 +789,96 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:15" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -941,34 +898,34 @@
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
       <c r="M10" s="7"/>
@@ -990,31 +947,31 @@
     </row>
     <row r="12" spans="1:15" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="26" t="s">
+      <c r="C12" s="34"/>
+      <c r="D12" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="33" t="s">
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="33" t="s">
+      <c r="J12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="33" t="s">
+      <c r="K12" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="32" t="s">
+      <c r="L12" s="34" t="s">
         <v>15</v>
       </c>
       <c r="M12" s="21"/>
@@ -1023,47 +980,47 @@
     </row>
     <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="32"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="34"/>
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="43"/>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
       <c r="M15" s="7"/>
@@ -1076,7 +1033,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="13"/>
-      <c r="H16" s="23"/>
+      <c r="H16" s="24"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
       <c r="K16" s="23"/>
@@ -1092,11 +1049,11 @@
       <c r="F17" s="6"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
-      <c r="I17" s="49" t="s">
+      <c r="I17" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
       <c r="L17" s="17"/>
       <c r="M17" s="11"/>
     </row>
@@ -1110,8 +1067,8 @@
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
       <c r="L18" s="6"/>
       <c r="M18" s="11"/>
     </row>
@@ -1123,13 +1080,13 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="20"/>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
       <c r="M19" s="15"/>
     </row>
     <row r="20" spans="1:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1139,7 +1096,7 @@
     <row r="26" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:13" s="12" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="L12:L13"/>
@@ -1150,7 +1107,6 @@
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="B5:L5"/>
-    <mergeCell ref="H16:L16"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:D10"/>
@@ -1165,6 +1121,5 @@
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/resources/report/60/95/ex_04ss/HD_04SS.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
   </si>
@@ -35,9 +35,6 @@
     <t>STT</t>
   </si>
   <si>
-    <t>Chúng tôi cam kết hoàn toàn chịu trách nhiệm trước pháp luật về tính chính xác, trung thực của nội dung nêu trên và thực hiện theo đúng quy định của pháp luật.</t>
-  </si>
-  <si>
     <t>NGƯỜI NỘP THUẾ</t>
   </si>
   <si>
@@ -78,13 +75,47 @@
   </si>
   <si>
     <t xml:space="preserve">Được ký bởi: </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Ghi chú:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2): Mã CQT cấp đối với hóa đơn có mã của CQT, hóa đơn không có mã của CQT để trống</t>
+    </r>
+  </si>
+  <si>
+    <t>Người nộp thuế thông báo về việc hóa đơn điện tử có sai sót như sau:</t>
+  </si>
+  <si>
+    <t>(Chữ ký số của người nộp thuế)</t>
+  </si>
+  <si>
+    <t>Signature Valid</t>
+  </si>
+  <si>
+    <t>Ngày ký:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,13 +144,6 @@
       <family val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -132,6 +156,41 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -141,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -271,32 +330,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -311,17 +344,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -331,142 +355,124 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -750,353 +756,412 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="1.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="4.85546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="4" customWidth="1"/>
-    <col min="10" max="12" width="12.7109375" style="4" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="4"/>
+    <col min="1" max="2" width="1.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="1" customWidth="1"/>
+    <col min="10" max="12" width="12.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.7109375" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="39" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="B5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="36"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="36"/>
+    </row>
+    <row r="14" spans="1:15" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="23"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="7"/>
-    </row>
-    <row r="3" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="7"/>
-    </row>
-    <row r="4" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="7"/>
-    </row>
-    <row r="5" spans="1:15" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="7"/>
-    </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="7"/>
-    </row>
-    <row r="12" spans="1:15" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-    </row>
-    <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="7"/>
-    </row>
-    <row r="14" spans="1:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="7"/>
-    </row>
-    <row r="15" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="11"/>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="11"/>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:13" s="12" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:13" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:13" s="12" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H23" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="34"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="24"/>
+    </row>
+    <row r="25" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:13" s="5" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="M12:M13"/>
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="L12:L13"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS.xlsx
@@ -1057,7 +1057,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="6"/>
       <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS.xlsx
@@ -115,7 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +180,13 @@
     </font>
     <font>
       <i/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
@@ -358,12 +365,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -430,50 +443,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -780,11 +787,11 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
       <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -795,96 +802,96 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
       <c r="M3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -904,148 +911,148 @@
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:15" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="14" t="s">
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="36"/>
+      <c r="M12" s="33"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="36"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="33"/>
     </row>
     <row r="14" spans="1:15" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="40"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="37"/>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="30"/>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1055,12 +1062,12 @@
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1070,14 +1077,14 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="8" t="s">
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1087,14 +1094,14 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="23" t="s">
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="23"/>
-      <c r="L19" s="22"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="24"/>
       <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1104,12 +1111,12 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="22"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="24"/>
       <c r="M20" s="3"/>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1119,15 +1126,14 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="31" t="s">
+      <c r="G21" s="7"/>
+      <c r="I21" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="3"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
@@ -1137,28 +1143,28 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="29" t="s">
+      <c r="I22" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="41"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
       <c r="L22" s="43"/>
-      <c r="M22" s="3"/>
+      <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H23" s="30" t="s">
+      <c r="I23" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="I23" s="34"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="24"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="2"/>
     </row>
     <row r="25" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:13" s="5" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:13" s="5" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:13" s="6" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="M12:M13"/>

--- a/resources/report/60/95/ex_04ss/HD_04SS.xlsx
+++ b/resources/report/60/95/ex_04ss/HD_04SS.xlsx
@@ -389,97 +389,97 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,9 +787,9 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="4"/>
@@ -802,96 +802,96 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
       <c r="M3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:15" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -911,34 +911,34 @@
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
       <c r="K10" s="12"/>
       <c r="L10" s="12"/>
       <c r="M10" s="4"/>
@@ -960,99 +960,99 @@
     </row>
     <row r="12" spans="1:15" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16" t="s">
+      <c r="C12" s="35"/>
+      <c r="D12" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="16" t="s">
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L12" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="33"/>
+      <c r="M12" s="37"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="33"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="37"/>
     </row>
     <row r="14" spans="1:15" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="37"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="30"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="23"/>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1096,12 +1096,12 @@
       <c r="F19" s="3"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="25" t="s">
+      <c r="I19" s="17"/>
+      <c r="J19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="25"/>
-      <c r="L19" s="24"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="17"/>
       <c r="M19" s="3"/>
     </row>
     <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1113,10 +1113,10 @@
       <c r="F20" s="3"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="24"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="17"/>
       <c r="M20" s="3"/>
     </row>
     <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1127,12 +1127,12 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="7"/>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="41"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="28"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="21"/>
       <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1143,21 +1143,21 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="4"/>
-      <c r="I22" s="39" t="s">
+      <c r="I22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="43"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="34"/>
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="32"/>
+      <c r="J23" s="25"/>
       <c r="K23" s="8"/>
-      <c r="L23" s="26"/>
+      <c r="L23" s="19"/>
       <c r="M23" s="2"/>
     </row>
     <row r="25" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1189,7 +1189,6 @@
     <mergeCell ref="J12:J13"/>
     <mergeCell ref="H12:H13"/>
   </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
